--- a/sheets/S08A22P203.xlsx
+++ b/sheets/S08A22P203.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8048" uniqueCount="1867">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8048" uniqueCount="1868">
   <si>
     <t>Voter ID</t>
   </si>
@@ -2618,6 +2618,9 @@
   </si>
   <si>
     <t>Phool Vati</t>
+  </si>
+  <si>
+    <t>HR/03/15/0318629</t>
   </si>
   <si>
     <t>Shishan Kumar</t>
@@ -16794,10 +16797,10 @@
     </row>
     <row r="416" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>812</v>
+        <v>869</v>
       </c>
       <c r="B416" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C416" t="s">
         <v>168</v>
@@ -16820,7 +16823,7 @@
     </row>
     <row r="417" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B417" t="s">
         <v>86</v>
@@ -16846,13 +16849,13 @@
     </row>
     <row r="418" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B418" t="s">
         <v>568</v>
       </c>
       <c r="C418" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D418" t="s">
         <v>11</v>
@@ -16872,10 +16875,10 @@
     </row>
     <row r="419" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B419" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C419" t="s">
         <v>86</v>
@@ -16898,13 +16901,13 @@
     </row>
     <row r="420" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B420" t="s">
         <v>327</v>
       </c>
       <c r="C420" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D420" t="s">
         <v>11</v>
@@ -16924,13 +16927,13 @@
     </row>
     <row r="421" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B421" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C421" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="D421" t="s">
         <v>11</v>
@@ -16950,13 +16953,13 @@
     </row>
     <row r="422" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B422" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C422" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="D422" t="s">
         <v>11</v>
@@ -16976,13 +16979,13 @@
     </row>
     <row r="423" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B423" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C423" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="D423" t="s">
         <v>11</v>
@@ -17002,13 +17005,13 @@
     </row>
     <row r="424" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B424" t="s">
         <v>293</v>
       </c>
       <c r="C424" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="D424" t="s">
         <v>11</v>
@@ -17028,7 +17031,7 @@
     </row>
     <row r="425" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B425" t="s">
         <v>154</v>
@@ -17054,13 +17057,13 @@
     </row>
     <row r="426" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B426" t="s">
         <v>102</v>
       </c>
       <c r="C426" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="D426" t="s">
         <v>11</v>
@@ -17080,7 +17083,7 @@
     </row>
     <row r="427" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B427" t="s">
         <v>170</v>
@@ -17106,13 +17109,13 @@
     </row>
     <row r="428" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B428" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C428" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="D428" t="s">
         <v>11</v>
@@ -17132,7 +17135,7 @@
     </row>
     <row r="429" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B429" t="s">
         <v>145</v>
@@ -17158,7 +17161,7 @@
     </row>
     <row r="430" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B430" t="s">
         <v>224</v>
@@ -17184,10 +17187,10 @@
     </row>
     <row r="431" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B431" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C431" t="s">
         <v>102</v>
@@ -17210,13 +17213,13 @@
     </row>
     <row r="432" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B432" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C432" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="D432" t="s">
         <v>11</v>
@@ -17236,7 +17239,7 @@
     </row>
     <row r="433" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B433" t="s">
         <v>333</v>
@@ -17262,13 +17265,13 @@
     </row>
     <row r="434" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B434" t="s">
         <v>404</v>
       </c>
       <c r="C434" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="D434" t="s">
         <v>11</v>
@@ -17288,10 +17291,10 @@
     </row>
     <row r="435" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B435" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C435" t="s">
         <v>614</v>
@@ -17314,13 +17317,13 @@
     </row>
     <row r="436" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B436" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C436" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="D436" t="s">
         <v>11</v>
@@ -17340,13 +17343,13 @@
     </row>
     <row r="437" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B437" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C437" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="D437" t="s">
         <v>11</v>
@@ -17366,13 +17369,13 @@
     </row>
     <row r="438" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B438" t="s">
         <v>581</v>
       </c>
       <c r="C438" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="D438" t="s">
         <v>11</v>
@@ -17392,13 +17395,13 @@
     </row>
     <row r="439" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B439" t="s">
         <v>278</v>
       </c>
       <c r="C439" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="D439" t="s">
         <v>11</v>
@@ -17418,7 +17421,7 @@
     </row>
     <row r="440" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B440" t="s">
         <v>224</v>
@@ -17444,13 +17447,13 @@
     </row>
     <row r="441" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B441" t="s">
         <v>83</v>
       </c>
       <c r="C441" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="D441" t="s">
         <v>11</v>
@@ -17470,7 +17473,7 @@
     </row>
     <row r="442" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B442" t="s">
         <v>85</v>
@@ -17496,13 +17499,13 @@
     </row>
     <row r="443" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B443" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C443" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D443" t="s">
         <v>11</v>
@@ -17522,7 +17525,7 @@
     </row>
     <row r="444" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B444" t="s">
         <v>33</v>
@@ -17548,13 +17551,13 @@
     </row>
     <row r="445" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B445" t="s">
         <v>327</v>
       </c>
       <c r="C445" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="D445" t="s">
         <v>11</v>
@@ -17574,10 +17577,10 @@
     </row>
     <row r="446" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B446" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C446" t="s">
         <v>614</v>
@@ -17600,10 +17603,10 @@
     </row>
     <row r="447" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B447" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="C447" t="s">
         <v>287</v>
@@ -17626,10 +17629,10 @@
     </row>
     <row r="448" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B448" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="C448" t="s">
         <v>327</v>
@@ -17652,13 +17655,13 @@
     </row>
     <row r="449" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B449" t="s">
         <v>219</v>
       </c>
       <c r="C449" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D449" t="s">
         <v>11</v>
@@ -17678,13 +17681,13 @@
     </row>
     <row r="450" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B450" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="C450" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="D450" t="s">
         <v>11</v>
@@ -17704,10 +17707,10 @@
     </row>
     <row r="451" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B451" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C451" t="s">
         <v>287</v>
@@ -17730,10 +17733,10 @@
     </row>
     <row r="452" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B452" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C452" t="s">
         <v>30</v>
@@ -17756,13 +17759,13 @@
     </row>
     <row r="453" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B453" t="s">
         <v>100</v>
       </c>
       <c r="C453" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="D453" t="s">
         <v>11</v>
@@ -17782,10 +17785,10 @@
     </row>
     <row r="454" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B454" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="C454" t="s">
         <v>610</v>
@@ -17808,10 +17811,10 @@
     </row>
     <row r="455" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B455" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="C455" t="s">
         <v>30</v>
@@ -17834,10 +17837,10 @@
     </row>
     <row r="456" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B456" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C456" t="s">
         <v>610</v>
@@ -17860,13 +17863,13 @@
     </row>
     <row r="457" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B457" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C457" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="D457" t="s">
         <v>11</v>
@@ -17886,10 +17889,10 @@
     </row>
     <row r="458" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B458" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="C458" t="s">
         <v>303</v>
@@ -17912,13 +17915,13 @@
     </row>
     <row r="459" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
+        <v>944</v>
+      </c>
+      <c r="B459" t="s">
+        <v>935</v>
+      </c>
+      <c r="C459" t="s">
         <v>943</v>
-      </c>
-      <c r="B459" t="s">
-        <v>934</v>
-      </c>
-      <c r="C459" t="s">
-        <v>942</v>
       </c>
       <c r="D459" t="s">
         <v>11</v>
@@ -17938,13 +17941,13 @@
     </row>
     <row r="460" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B460" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="C460" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="D460" t="s">
         <v>11</v>
@@ -17964,13 +17967,13 @@
     </row>
     <row r="461" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
+        <v>948</v>
+      </c>
+      <c r="B461" t="s">
+        <v>949</v>
+      </c>
+      <c r="C461" t="s">
         <v>947</v>
-      </c>
-      <c r="B461" t="s">
-        <v>948</v>
-      </c>
-      <c r="C461" t="s">
-        <v>946</v>
       </c>
       <c r="D461" t="s">
         <v>11</v>
@@ -17990,13 +17993,13 @@
     </row>
     <row r="462" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B462" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="C462" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="D462" t="s">
         <v>11</v>
@@ -18016,13 +18019,13 @@
     </row>
     <row r="463" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B463" t="s">
         <v>411</v>
       </c>
       <c r="C463" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="D463" t="s">
         <v>11</v>
@@ -18042,13 +18045,13 @@
     </row>
     <row r="464" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B464" t="s">
         <v>482</v>
       </c>
       <c r="C464" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="D464" t="s">
         <v>11</v>
@@ -18068,13 +18071,13 @@
     </row>
     <row r="465" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B465" t="s">
         <v>565</v>
       </c>
       <c r="C465" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="D465" t="s">
         <v>11</v>
@@ -18094,10 +18097,10 @@
     </row>
     <row r="466" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B466" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="C466" t="s">
         <v>565</v>
@@ -18120,7 +18123,7 @@
     </row>
     <row r="467" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B467" t="s">
         <v>510</v>
@@ -18146,13 +18149,13 @@
     </row>
     <row r="468" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B468" t="s">
         <v>159</v>
       </c>
       <c r="C468" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="D468" t="s">
         <v>11</v>
@@ -18172,13 +18175,13 @@
     </row>
     <row r="469" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B469" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C469" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="D469" t="s">
         <v>11</v>
@@ -18198,13 +18201,13 @@
     </row>
     <row r="470" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B470" t="s">
         <v>865</v>
       </c>
       <c r="C470" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="D470" t="s">
         <v>11</v>
@@ -18224,7 +18227,7 @@
     </row>
     <row r="471" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B471" t="s">
         <v>100</v>
@@ -18250,7 +18253,7 @@
     </row>
     <row r="472" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B472" t="s">
         <v>17</v>
@@ -18276,13 +18279,13 @@
     </row>
     <row r="473" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B473" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C473" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="D473" t="s">
         <v>11</v>
@@ -18302,13 +18305,13 @@
     </row>
     <row r="474" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
+        <v>967</v>
+      </c>
+      <c r="B474" t="s">
+        <v>968</v>
+      </c>
+      <c r="C474" t="s">
         <v>966</v>
-      </c>
-      <c r="B474" t="s">
-        <v>967</v>
-      </c>
-      <c r="C474" t="s">
-        <v>965</v>
       </c>
       <c r="D474" t="s">
         <v>11</v>
@@ -18328,10 +18331,10 @@
     </row>
     <row r="475" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B475" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="C475" t="s">
         <v>420</v>
@@ -18354,13 +18357,13 @@
     </row>
     <row r="476" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B476" t="s">
         <v>397</v>
       </c>
       <c r="C476" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="D476" t="s">
         <v>11</v>
@@ -18380,13 +18383,13 @@
     </row>
     <row r="477" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B477" t="s">
         <v>27</v>
       </c>
       <c r="C477" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="D477" t="s">
         <v>11</v>
@@ -18406,7 +18409,7 @@
     </row>
     <row r="478" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B478" t="s">
         <v>417</v>
@@ -18432,13 +18435,13 @@
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B479" t="s">
         <v>327</v>
       </c>
       <c r="C479" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="D479" t="s">
         <v>11</v>
@@ -18458,13 +18461,13 @@
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B480" t="s">
         <v>585</v>
       </c>
       <c r="C480" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="D480" t="s">
         <v>11</v>
@@ -18484,10 +18487,10 @@
     </row>
     <row r="481" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B481" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C481" t="s">
         <v>97</v>
@@ -18510,13 +18513,13 @@
     </row>
     <row r="482" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B482" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="C482" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="D482" t="s">
         <v>11</v>
@@ -18536,13 +18539,13 @@
     </row>
     <row r="483" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B483" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C483" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="D483" t="s">
         <v>11</v>
@@ -18562,13 +18565,13 @@
     </row>
     <row r="484" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
+        <v>983</v>
+      </c>
+      <c r="B484" t="s">
+        <v>984</v>
+      </c>
+      <c r="C484" t="s">
         <v>982</v>
-      </c>
-      <c r="B484" t="s">
-        <v>983</v>
-      </c>
-      <c r="C484" t="s">
-        <v>981</v>
       </c>
       <c r="D484" t="s">
         <v>11</v>
@@ -18588,13 +18591,13 @@
     </row>
     <row r="485" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B485" t="s">
         <v>55</v>
       </c>
       <c r="C485" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="D485" t="s">
         <v>11</v>
@@ -18614,10 +18617,10 @@
     </row>
     <row r="486" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B486" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="C486" t="s">
         <v>198</v>
@@ -18640,10 +18643,10 @@
     </row>
     <row r="487" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B487" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="C487" t="s">
         <v>198</v>
@@ -18666,7 +18669,7 @@
     </row>
     <row r="488" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B488" t="s">
         <v>596</v>
@@ -18692,13 +18695,13 @@
     </row>
     <row r="489" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B489" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="C489" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="D489" t="s">
         <v>11</v>
@@ -18718,13 +18721,13 @@
     </row>
     <row r="490" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B490" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="C490" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="D490" t="s">
         <v>11</v>
@@ -18744,13 +18747,13 @@
     </row>
     <row r="491" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B491" t="s">
         <v>612</v>
       </c>
       <c r="C491" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="D491" t="s">
         <v>11</v>
@@ -18770,13 +18773,13 @@
     </row>
     <row r="492" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B492" t="s">
         <v>413</v>
       </c>
       <c r="C492" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="D492" t="s">
         <v>11</v>
@@ -18796,7 +18799,7 @@
     </row>
     <row r="493" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B493" t="s">
         <v>145</v>
@@ -18822,13 +18825,13 @@
     </row>
     <row r="494" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B494" t="s">
         <v>170</v>
       </c>
       <c r="C494" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="D494" t="s">
         <v>11</v>
@@ -18848,10 +18851,10 @@
     </row>
     <row r="495" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B495" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="C495" t="s">
         <v>170</v>
@@ -18874,13 +18877,13 @@
     </row>
     <row r="496" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B496" t="s">
         <v>648</v>
       </c>
       <c r="C496" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="D496" t="s">
         <v>11</v>
@@ -18900,10 +18903,10 @@
     </row>
     <row r="497" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B497" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="C497" t="s">
         <v>648</v>
@@ -18926,10 +18929,10 @@
     </row>
     <row r="498" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B498" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="C498" t="s">
         <v>413</v>
@@ -18952,13 +18955,13 @@
     </row>
     <row r="499" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B499" t="s">
         <v>365</v>
       </c>
       <c r="C499" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="D499" t="s">
         <v>11</v>
@@ -18978,13 +18981,13 @@
     </row>
     <row r="500" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B500" t="s">
         <v>97</v>
       </c>
       <c r="C500" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="D500" t="s">
         <v>11</v>
@@ -19004,7 +19007,7 @@
     </row>
     <row r="501" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B501" t="s">
         <v>100</v>
@@ -19030,13 +19033,13 @@
     </row>
     <row r="502" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B502" t="s">
         <v>102</v>
       </c>
       <c r="C502" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="D502" t="s">
         <v>11</v>
@@ -19056,10 +19059,10 @@
     </row>
     <row r="503" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B503" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C503" t="s">
         <v>102</v>
@@ -19082,13 +19085,13 @@
     </row>
     <row r="504" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B504" t="s">
         <v>431</v>
       </c>
       <c r="C504" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="D504" t="s">
         <v>11</v>
@@ -19108,7 +19111,7 @@
     </row>
     <row r="505" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B505" t="s">
         <v>568</v>
@@ -19134,13 +19137,13 @@
     </row>
     <row r="506" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B506" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="C506" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="D506" t="s">
         <v>11</v>
@@ -19160,13 +19163,13 @@
     </row>
     <row r="507" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B507" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="C507" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="D507" t="s">
         <v>11</v>
@@ -19186,13 +19189,13 @@
     </row>
     <row r="508" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B508" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="C508" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="D508" t="s">
         <v>11</v>
@@ -19212,13 +19215,13 @@
     </row>
     <row r="509" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B509" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="C509" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="D509" t="s">
         <v>11</v>
@@ -19238,13 +19241,13 @@
     </row>
     <row r="510" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B510" t="s">
         <v>433</v>
       </c>
       <c r="C510" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="D510" t="s">
         <v>11</v>
@@ -19264,13 +19267,13 @@
     </row>
     <row r="511" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B511" t="s">
         <v>58</v>
       </c>
       <c r="C511" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="D511" t="s">
         <v>11</v>
@@ -19290,7 +19293,7 @@
     </row>
     <row r="512" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B512" t="s">
         <v>232</v>
@@ -19316,10 +19319,10 @@
     </row>
     <row r="513" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B513" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="C513" t="s">
         <v>388</v>
@@ -19342,13 +19345,13 @@
     </row>
     <row r="514" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B514" t="s">
         <v>420</v>
       </c>
       <c r="C514" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="D514" t="s">
         <v>11</v>
@@ -19368,10 +19371,10 @@
     </row>
     <row r="515" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B515" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="C515" t="s">
         <v>388</v>
@@ -19394,13 +19397,13 @@
     </row>
     <row r="516" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B516" t="s">
         <v>671</v>
       </c>
       <c r="C516" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="D516" t="s">
         <v>11</v>
@@ -19420,13 +19423,13 @@
     </row>
     <row r="517" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B517" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="C517" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="D517" t="s">
         <v>11</v>
@@ -19446,13 +19449,13 @@
     </row>
     <row r="518" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B518" t="s">
         <v>297</v>
       </c>
       <c r="C518" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="D518" t="s">
         <v>11</v>
@@ -19472,13 +19475,13 @@
     </row>
     <row r="519" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B519" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C519" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="D519" t="s">
         <v>11</v>
@@ -19498,10 +19501,10 @@
     </row>
     <row r="520" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B520" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="C520" t="s">
         <v>118</v>
@@ -19524,10 +19527,10 @@
     </row>
     <row r="521" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B521" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="C521" t="s">
         <v>299</v>
@@ -19550,13 +19553,13 @@
     </row>
     <row r="522" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B522" t="s">
         <v>100</v>
       </c>
       <c r="C522" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="D522" t="s">
         <v>11</v>
@@ -19576,13 +19579,13 @@
     </row>
     <row r="523" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B523" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="C523" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="D523" t="s">
         <v>11</v>
@@ -19602,13 +19605,13 @@
     </row>
     <row r="524" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B524" t="s">
         <v>457</v>
       </c>
       <c r="C524" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="D524" t="s">
         <v>11</v>
@@ -19628,13 +19631,13 @@
     </row>
     <row r="525" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B525" t="s">
         <v>491</v>
       </c>
       <c r="C525" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="D525" t="s">
         <v>11</v>
@@ -19654,7 +19657,7 @@
     </row>
     <row r="526" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B526" t="s">
         <v>652</v>
@@ -19680,10 +19683,10 @@
     </row>
     <row r="527" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B527" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C527" t="s">
         <v>40</v>
@@ -19706,10 +19709,10 @@
     </row>
     <row r="528" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B528" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="C528" t="s">
         <v>263</v>
@@ -19732,13 +19735,13 @@
     </row>
     <row r="529" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B529" t="s">
         <v>251</v>
       </c>
       <c r="C529" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="D529" t="s">
         <v>11</v>
@@ -19758,10 +19761,10 @@
     </row>
     <row r="530" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B530" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="C530" t="s">
         <v>263</v>
@@ -19784,13 +19787,13 @@
     </row>
     <row r="531" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B531" t="s">
         <v>27</v>
       </c>
       <c r="C531" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="D531" t="s">
         <v>11</v>
@@ -19810,13 +19813,13 @@
     </row>
     <row r="532" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B532" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="C532" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="D532" t="s">
         <v>11</v>
@@ -19836,13 +19839,13 @@
     </row>
     <row r="533" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B533" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="C533" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="D533" t="s">
         <v>11</v>
@@ -19862,10 +19865,10 @@
     </row>
     <row r="534" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B534" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="C534" t="s">
         <v>40</v>
@@ -19888,13 +19891,13 @@
     </row>
     <row r="535" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B535" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="C535" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="D535" t="s">
         <v>11</v>
@@ -19914,13 +19917,13 @@
     </row>
     <row r="536" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B536" t="s">
         <v>355</v>
       </c>
       <c r="C536" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="D536" t="s">
         <v>11</v>
@@ -19940,13 +19943,13 @@
     </row>
     <row r="537" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B537" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C537" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="D537" t="s">
         <v>11</v>
@@ -19966,13 +19969,13 @@
     </row>
     <row r="538" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="B538" t="s">
         <v>188</v>
       </c>
       <c r="C538" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="D538" t="s">
         <v>11</v>
@@ -19992,13 +19995,13 @@
     </row>
     <row r="539" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B539" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="C539" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="D539" t="s">
         <v>11</v>
@@ -20018,13 +20021,13 @@
     </row>
     <row r="540" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B540" t="s">
         <v>728</v>
       </c>
       <c r="C540" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="D540" t="s">
         <v>11</v>
@@ -20044,13 +20047,13 @@
     </row>
     <row r="541" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B541" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="C541" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="D541" t="s">
         <v>11</v>
@@ -20070,7 +20073,7 @@
     </row>
     <row r="542" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B542" t="s">
         <v>766</v>
@@ -20096,13 +20099,13 @@
     </row>
     <row r="543" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="B543" t="s">
         <v>74</v>
       </c>
       <c r="C543" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="D543" t="s">
         <v>11</v>
@@ -20122,13 +20125,13 @@
     </row>
     <row r="544" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B544" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="C544" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="D544" t="s">
         <v>11</v>
@@ -20148,10 +20151,10 @@
     </row>
     <row r="545" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B545" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="C545" t="s">
         <v>766</v>
@@ -20174,13 +20177,13 @@
     </row>
     <row r="546" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B546" t="s">
         <v>297</v>
       </c>
       <c r="C546" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="D546" t="s">
         <v>11</v>
@@ -20200,7 +20203,7 @@
     </row>
     <row r="547" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="B547" t="s">
         <v>10</v>
@@ -20226,10 +20229,10 @@
     </row>
     <row r="548" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B548" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="C548" t="s">
         <v>203</v>
@@ -20252,10 +20255,10 @@
     </row>
     <row r="549" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B549" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="C549" t="s">
         <v>203</v>
@@ -20278,7 +20281,7 @@
     </row>
     <row r="550" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B550" t="s">
         <v>356</v>
@@ -20304,10 +20307,10 @@
     </row>
     <row r="551" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B551" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="C551" t="s">
         <v>71</v>
@@ -20330,13 +20333,13 @@
     </row>
     <row r="552" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B552" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="C552" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="D552" t="s">
         <v>11</v>
@@ -20356,10 +20359,10 @@
     </row>
     <row r="553" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B553" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="C553" t="s">
         <v>356</v>
@@ -20382,13 +20385,13 @@
     </row>
     <row r="554" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B554" t="s">
         <v>488</v>
       </c>
       <c r="C554" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="D554" t="s">
         <v>11</v>
@@ -20408,10 +20411,10 @@
     </row>
     <row r="555" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B555" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="C555" t="s">
         <v>71</v>
@@ -20434,13 +20437,13 @@
     </row>
     <row r="556" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B556" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="C556" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="D556" t="s">
         <v>11</v>
@@ -20460,13 +20463,13 @@
     </row>
     <row r="557" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B557" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C557" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="D557" t="s">
         <v>11</v>
@@ -20486,13 +20489,13 @@
     </row>
     <row r="558" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B558" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C558" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D558" t="s">
         <v>11</v>
@@ -20512,10 +20515,10 @@
     </row>
     <row r="559" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B559" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="C559" t="s">
         <v>407</v>
@@ -20538,10 +20541,10 @@
     </row>
     <row r="560" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B560" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="C560" t="s">
         <v>407</v>
@@ -20564,13 +20567,13 @@
     </row>
     <row r="561" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B561" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="C561" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="D561" t="s">
         <v>11</v>
@@ -20590,13 +20593,13 @@
     </row>
     <row r="562" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="B562" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="C562" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="D562" t="s">
         <v>11</v>
@@ -20616,13 +20619,13 @@
     </row>
     <row r="563" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B563" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="C563" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="D563" t="s">
         <v>11</v>
@@ -20642,13 +20645,13 @@
     </row>
     <row r="564" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B564" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C564" t="s">
         <v>1128</v>
-      </c>
-      <c r="B564" t="s">
-        <v>1129</v>
-      </c>
-      <c r="C564" t="s">
-        <v>1127</v>
       </c>
       <c r="D564" t="s">
         <v>11</v>
@@ -20668,13 +20671,13 @@
     </row>
     <row r="565" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="B565" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="C565" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="D565" t="s">
         <v>11</v>
@@ -20694,13 +20697,13 @@
     </row>
     <row r="566" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B566" t="s">
         <v>154</v>
       </c>
       <c r="C566" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="D566" t="s">
         <v>11</v>
@@ -20720,13 +20723,13 @@
     </row>
     <row r="567" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B567" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="C567" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="D567" t="s">
         <v>11</v>
@@ -20746,13 +20749,13 @@
     </row>
     <row r="568" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B568" t="s">
         <v>706</v>
       </c>
       <c r="C568" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="D568" t="s">
         <v>11</v>
@@ -20772,13 +20775,13 @@
     </row>
     <row r="569" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B569" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="C569" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="D569" t="s">
         <v>11</v>
@@ -20798,13 +20801,13 @@
     </row>
     <row r="570" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B570" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="C570" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="D570" t="s">
         <v>11</v>
@@ -20824,13 +20827,13 @@
     </row>
     <row r="571" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B571" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="C571" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="D571" t="s">
         <v>11</v>
@@ -20850,13 +20853,13 @@
     </row>
     <row r="572" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B572" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="C572" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="D572" t="s">
         <v>11</v>
@@ -20876,13 +20879,13 @@
     </row>
     <row r="573" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B573" t="s">
         <v>156</v>
       </c>
       <c r="C573" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="D573" t="s">
         <v>11</v>
@@ -20902,13 +20905,13 @@
     </row>
     <row r="574" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B574" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C574" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="D574" t="s">
         <v>11</v>
@@ -20928,13 +20931,13 @@
     </row>
     <row r="575" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="B575" t="s">
         <v>276</v>
       </c>
       <c r="C575" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="D575" t="s">
         <v>11</v>
@@ -20954,13 +20957,13 @@
     </row>
     <row r="576" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B576" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C576" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="D576" t="s">
         <v>11</v>
@@ -20980,13 +20983,13 @@
     </row>
     <row r="577" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B577" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="C577" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="D577" t="s">
         <v>11</v>
@@ -21006,13 +21009,13 @@
     </row>
     <row r="578" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B578" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="C578" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="D578" t="s">
         <v>11</v>
@@ -21032,13 +21035,13 @@
     </row>
     <row r="579" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B579" t="s">
         <v>718</v>
       </c>
       <c r="C579" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="D579" t="s">
         <v>11</v>
@@ -21058,10 +21061,10 @@
     </row>
     <row r="580" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="B580" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="C580" t="s">
         <v>718</v>
@@ -21084,13 +21087,13 @@
     </row>
     <row r="581" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="B581" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="C581" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="D581" t="s">
         <v>11</v>
@@ -21110,13 +21113,13 @@
     </row>
     <row r="582" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B582" t="s">
         <v>1162</v>
       </c>
-      <c r="B582" t="s">
-        <v>1161</v>
-      </c>
       <c r="C582" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="D582" t="s">
         <v>11</v>
@@ -21136,13 +21139,13 @@
     </row>
     <row r="583" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B583" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="C583" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="D583" t="s">
         <v>11</v>
@@ -21162,13 +21165,13 @@
     </row>
     <row r="584" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="B584" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="C584" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="D584" t="s">
         <v>11</v>
@@ -21188,13 +21191,13 @@
     </row>
     <row r="585" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="B585" t="s">
         <v>205</v>
       </c>
       <c r="C585" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="D585" t="s">
         <v>11</v>
@@ -21214,10 +21217,10 @@
     </row>
     <row r="586" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="B586" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="C586" t="s">
         <v>433</v>
@@ -21240,13 +21243,13 @@
     </row>
     <row r="587" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="B587" t="s">
         <v>333</v>
       </c>
       <c r="C587" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="D587" t="s">
         <v>11</v>
@@ -21266,10 +21269,10 @@
     </row>
     <row r="588" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="B588" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="C588" t="s">
         <v>366</v>
@@ -21292,10 +21295,10 @@
     </row>
     <row r="589" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B589" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="C589" t="s">
         <v>460</v>
@@ -21318,13 +21321,13 @@
     </row>
     <row r="590" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="B590" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="C590" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="D590" t="s">
         <v>11</v>
@@ -21344,13 +21347,13 @@
     </row>
     <row r="591" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="B591" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="C591" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="D591" t="s">
         <v>11</v>
@@ -21370,13 +21373,13 @@
     </row>
     <row r="592" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="B592" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C592" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="D592" t="s">
         <v>11</v>
@@ -21396,13 +21399,13 @@
     </row>
     <row r="593" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B593" t="s">
         <v>488</v>
       </c>
       <c r="C593" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="D593" t="s">
         <v>11</v>
@@ -21422,13 +21425,13 @@
     </row>
     <row r="594" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B594" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="C594" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="D594" t="s">
         <v>11</v>
@@ -21448,13 +21451,13 @@
     </row>
     <row r="595" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="B595" t="s">
         <v>565</v>
       </c>
       <c r="C595" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="D595" t="s">
         <v>11</v>
@@ -21474,13 +21477,13 @@
     </row>
     <row r="596" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B596" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="C596" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="D596" t="s">
         <v>11</v>
@@ -21500,10 +21503,10 @@
     </row>
     <row r="597" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="B597" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="C597" t="s">
         <v>833</v>
@@ -21526,7 +21529,7 @@
     </row>
     <row r="598" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="B598" t="s">
         <v>433</v>
@@ -21552,13 +21555,13 @@
     </row>
     <row r="599" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="B599" t="s">
         <v>351</v>
       </c>
       <c r="C599" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="D599" t="s">
         <v>11</v>
@@ -21578,13 +21581,13 @@
     </row>
     <row r="600" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="B600" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="C600" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="D600" t="s">
         <v>11</v>
@@ -21604,10 +21607,10 @@
     </row>
     <row r="601" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="B601" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="C601" t="s">
         <v>351</v>
@@ -21630,7 +21633,7 @@
     </row>
     <row r="602" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="B602" t="s">
         <v>74</v>
@@ -21656,10 +21659,10 @@
     </row>
     <row r="603" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="B603" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="C603" t="s">
         <v>499</v>
@@ -21682,10 +21685,10 @@
     </row>
     <row r="604" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="B604" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C604" t="s">
         <v>351</v>
@@ -21708,13 +21711,13 @@
     </row>
     <row r="605" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="B605" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="C605" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="D605" t="s">
         <v>11</v>
@@ -21734,10 +21737,10 @@
     </row>
     <row r="606" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="B606" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="C606" t="s">
         <v>726</v>
@@ -21760,13 +21763,13 @@
     </row>
     <row r="607" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="B607" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="C607" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="D607" t="s">
         <v>11</v>
@@ -21786,13 +21789,13 @@
     </row>
     <row r="608" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="B608" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="C608" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="D608" t="s">
         <v>11</v>
@@ -21812,13 +21815,13 @@
     </row>
     <row r="609" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="B609" t="s">
         <v>726</v>
       </c>
       <c r="C609" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="D609" t="s">
         <v>11</v>
@@ -21838,7 +21841,7 @@
     </row>
     <row r="610" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B610" t="s">
         <v>224</v>
@@ -21864,7 +21867,7 @@
     </row>
     <row r="611" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="B611" t="s">
         <v>282</v>
@@ -21890,13 +21893,13 @@
     </row>
     <row r="612" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B612" t="s">
         <v>614</v>
       </c>
       <c r="C612" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="D612" t="s">
         <v>11</v>
@@ -21916,13 +21919,13 @@
     </row>
     <row r="613" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="B613" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="C613" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="D613" t="s">
         <v>11</v>
@@ -21942,13 +21945,13 @@
     </row>
     <row r="614" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B614" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C614" t="s">
         <v>1220</v>
-      </c>
-      <c r="B614" t="s">
-        <v>1221</v>
-      </c>
-      <c r="C614" t="s">
-        <v>1219</v>
       </c>
       <c r="D614" t="s">
         <v>11</v>
@@ -21968,13 +21971,13 @@
     </row>
     <row r="615" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B615" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="C615" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="D615" t="s">
         <v>11</v>
@@ -21994,13 +21997,13 @@
     </row>
     <row r="616" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B616" t="s">
         <v>766</v>
       </c>
       <c r="C616" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="D616" t="s">
         <v>11</v>
@@ -22020,7 +22023,7 @@
     </row>
     <row r="617" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="B617" t="s">
         <v>365</v>
@@ -22046,13 +22049,13 @@
     </row>
     <row r="618" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="B618" t="s">
         <v>143</v>
       </c>
       <c r="C618" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="D618" t="s">
         <v>11</v>
@@ -22072,7 +22075,7 @@
     </row>
     <row r="619" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="B619" t="s">
         <v>510</v>
@@ -22098,13 +22101,13 @@
     </row>
     <row r="620" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B620" t="s">
         <v>317</v>
       </c>
       <c r="C620" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="D620" t="s">
         <v>11</v>
@@ -22124,7 +22127,7 @@
     </row>
     <row r="621" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="B621" t="s">
         <v>100</v>
@@ -22150,13 +22153,13 @@
     </row>
     <row r="622" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B622" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="C622" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D622" t="s">
         <v>11</v>
@@ -22176,13 +22179,13 @@
     </row>
     <row r="623" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B623" t="s">
         <v>45</v>
       </c>
       <c r="C623" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="D623" t="s">
         <v>11</v>
@@ -22202,13 +22205,13 @@
     </row>
     <row r="624" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="B624" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="C624" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="D624" t="s">
         <v>11</v>
@@ -22228,10 +22231,10 @@
     </row>
     <row r="625" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="B625" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="C625" t="s">
         <v>168</v>
@@ -22254,10 +22257,10 @@
     </row>
     <row r="626" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="B626" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="C626" t="s">
         <v>168</v>
@@ -22280,13 +22283,13 @@
     </row>
     <row r="627" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B627" t="s">
         <v>100</v>
       </c>
       <c r="C627" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="D627" t="s">
         <v>11</v>
@@ -22306,13 +22309,13 @@
     </row>
     <row r="628" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="B628" t="s">
         <v>545</v>
       </c>
       <c r="C628" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="D628" t="s">
         <v>11</v>
@@ -22332,10 +22335,10 @@
     </row>
     <row r="629" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B629" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="C629" t="s">
         <v>545</v>
@@ -22358,10 +22361,10 @@
     </row>
     <row r="630" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="B630" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="C630" t="s">
         <v>545</v>
@@ -22384,13 +22387,13 @@
     </row>
     <row r="631" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="B631" t="s">
         <v>466</v>
       </c>
       <c r="C631" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="D631" t="s">
         <v>11</v>
@@ -22410,13 +22413,13 @@
     </row>
     <row r="632" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="B632" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="C632" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="D632" t="s">
         <v>11</v>
@@ -22436,10 +22439,10 @@
     </row>
     <row r="633" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B633" t="s">
         <v>1253</v>
-      </c>
-      <c r="B633" t="s">
-        <v>1252</v>
       </c>
       <c r="C633" t="s">
         <v>71</v>
@@ -22462,13 +22465,13 @@
     </row>
     <row r="634" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B634" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="C634" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="D634" t="s">
         <v>11</v>
@@ -22488,13 +22491,13 @@
     </row>
     <row r="635" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B635" t="s">
         <v>441</v>
       </c>
       <c r="C635" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="D635" t="s">
         <v>11</v>
@@ -22514,7 +22517,7 @@
     </row>
     <row r="636" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="B636" t="s">
         <v>711</v>
@@ -22540,13 +22543,13 @@
     </row>
     <row r="637" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="B637" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="C637" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="D637" t="s">
         <v>11</v>
@@ -22566,13 +22569,13 @@
     </row>
     <row r="638" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="B638" t="s">
         <v>439</v>
       </c>
       <c r="C638" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="D638" t="s">
         <v>11</v>
@@ -22592,10 +22595,10 @@
     </row>
     <row r="639" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="B639" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="C639" t="s">
         <v>439</v>
@@ -22618,13 +22621,13 @@
     </row>
     <row r="640" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="B640" t="s">
         <v>654</v>
       </c>
       <c r="C640" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="D640" t="s">
         <v>11</v>
@@ -22644,10 +22647,10 @@
     </row>
     <row r="641" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B641" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="C641" t="s">
         <v>654</v>
@@ -22670,13 +22673,13 @@
     </row>
     <row r="642" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B642" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="C642" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="D642" t="s">
         <v>11</v>
@@ -22696,13 +22699,13 @@
     </row>
     <row r="643" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="B643" t="s">
         <v>402</v>
       </c>
       <c r="C643" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="D643" t="s">
         <v>11</v>
@@ -22722,13 +22725,13 @@
     </row>
     <row r="644" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B644" t="s">
         <v>180</v>
       </c>
       <c r="C644" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="D644" t="s">
         <v>11</v>
@@ -22748,10 +22751,10 @@
     </row>
     <row r="645" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="B645" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="C645" t="s">
         <v>654</v>
@@ -22774,7 +22777,7 @@
     </row>
     <row r="646" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B646" t="s">
         <v>251</v>
@@ -22800,10 +22803,10 @@
     </row>
     <row r="647" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B647" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="C647" t="s">
         <v>180</v>
@@ -22826,13 +22829,13 @@
     </row>
     <row r="648" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="B648" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="C648" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="D648" t="s">
         <v>11</v>
@@ -22852,7 +22855,7 @@
     </row>
     <row r="649" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="B649" t="s">
         <v>282</v>
@@ -22878,13 +22881,13 @@
     </row>
     <row r="650" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="B650" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="C650" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="D650" t="s">
         <v>11</v>
@@ -22904,13 +22907,13 @@
     </row>
     <row r="651" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B651" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="C651" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="D651" t="s">
         <v>11</v>
@@ -22930,13 +22933,13 @@
     </row>
     <row r="652" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="B652" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C652" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="D652" t="s">
         <v>11</v>
@@ -22956,13 +22959,13 @@
     </row>
     <row r="653" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B653" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="C653" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="D653" t="s">
         <v>11</v>
@@ -22982,7 +22985,7 @@
     </row>
     <row r="654" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="B654" t="s">
         <v>246</v>
@@ -23008,10 +23011,10 @@
     </row>
     <row r="655" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="B655" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="C655" t="s">
         <v>614</v>
@@ -23034,7 +23037,7 @@
     </row>
     <row r="656" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="B656" t="s">
         <v>397</v>
@@ -23060,13 +23063,13 @@
     </row>
     <row r="657" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="B657" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="C657" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="D657" t="s">
         <v>11</v>
@@ -23086,10 +23089,10 @@
     </row>
     <row r="658" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="B658" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="C658" t="s">
         <v>373</v>
@@ -23112,13 +23115,13 @@
     </row>
     <row r="659" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="B659" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="C659" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="D659" t="s">
         <v>11</v>
@@ -23138,7 +23141,7 @@
     </row>
     <row r="660" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="B660" t="s">
         <v>383</v>
@@ -23164,13 +23167,13 @@
     </row>
     <row r="661" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="B661" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="C661" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="D661" t="s">
         <v>11</v>
@@ -23190,13 +23193,13 @@
     </row>
     <row r="662" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B662" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C662" t="s">
         <v>1300</v>
-      </c>
-      <c r="B662" t="s">
-        <v>1301</v>
-      </c>
-      <c r="C662" t="s">
-        <v>1299</v>
       </c>
       <c r="D662" t="s">
         <v>11</v>
@@ -23216,13 +23219,13 @@
     </row>
     <row r="663" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="B663" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="C663" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="D663" t="s">
         <v>11</v>
@@ -23242,10 +23245,10 @@
     </row>
     <row r="664" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="B664" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="C664" t="s">
         <v>713</v>
@@ -23268,13 +23271,13 @@
     </row>
     <row r="665" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="B665" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="C665" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="D665" t="s">
         <v>11</v>
@@ -23294,13 +23297,13 @@
     </row>
     <row r="666" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="B666" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="C666" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="D666" t="s">
         <v>11</v>
@@ -23320,13 +23323,13 @@
     </row>
     <row r="667" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B667" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C667" t="s">
         <v>1310</v>
-      </c>
-      <c r="B667" t="s">
-        <v>1311</v>
-      </c>
-      <c r="C667" t="s">
-        <v>1309</v>
       </c>
       <c r="D667" t="s">
         <v>11</v>
@@ -23346,13 +23349,13 @@
     </row>
     <row r="668" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="B668" t="s">
         <v>488</v>
       </c>
       <c r="C668" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="D668" t="s">
         <v>11</v>
@@ -23372,13 +23375,13 @@
     </row>
     <row r="669" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="B669" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="C669" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="D669" t="s">
         <v>11</v>
@@ -23398,13 +23401,13 @@
     </row>
     <row r="670" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="B670" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="C670" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="D670" t="s">
         <v>11</v>
@@ -23424,13 +23427,13 @@
     </row>
     <row r="671" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="B671" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="C671" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="D671" t="s">
         <v>11</v>
@@ -23450,13 +23453,13 @@
     </row>
     <row r="672" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B672" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C672" t="s">
         <v>1320</v>
-      </c>
-      <c r="B672" t="s">
-        <v>1321</v>
-      </c>
-      <c r="C672" t="s">
-        <v>1319</v>
       </c>
       <c r="D672" t="s">
         <v>11</v>
@@ -23476,13 +23479,13 @@
     </row>
     <row r="673" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B673" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="C673" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="D673" t="s">
         <v>11</v>
@@ -23502,13 +23505,13 @@
     </row>
     <row r="674" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="B674" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="C674" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="D674" t="s">
         <v>11</v>
@@ -23528,10 +23531,10 @@
     </row>
     <row r="675" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="B675" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="C675" t="s">
         <v>219</v>
@@ -23554,13 +23557,13 @@
     </row>
     <row r="676" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="B676" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="C676" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="D676" t="s">
         <v>11</v>
@@ -23580,13 +23583,13 @@
     </row>
     <row r="677" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="B677" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="C677" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="D677" t="s">
         <v>11</v>
@@ -23606,13 +23609,13 @@
     </row>
     <row r="678" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="B678" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="C678" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="D678" t="s">
         <v>11</v>
@@ -23632,13 +23635,13 @@
     </row>
     <row r="679" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="B679" t="s">
         <v>219</v>
       </c>
       <c r="C679" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="D679" t="s">
         <v>11</v>
@@ -23658,13 +23661,13 @@
     </row>
     <row r="680" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="B680" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="C680" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="D680" t="s">
         <v>11</v>
@@ -23684,13 +23687,13 @@
     </row>
     <row r="681" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="B681" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="C681" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="D681" t="s">
         <v>11</v>
@@ -23710,13 +23713,13 @@
     </row>
     <row r="682" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="B682" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="C682" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="D682" t="s">
         <v>11</v>
@@ -23736,13 +23739,13 @@
     </row>
     <row r="683" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B683" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C683" t="s">
         <v>1343</v>
-      </c>
-      <c r="B683" t="s">
-        <v>1344</v>
-      </c>
-      <c r="C683" t="s">
-        <v>1342</v>
       </c>
       <c r="D683" t="s">
         <v>11</v>
@@ -23762,13 +23765,13 @@
     </row>
     <row r="684" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="B684" t="s">
         <v>40</v>
       </c>
       <c r="C684" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="D684" t="s">
         <v>11</v>
@@ -23788,13 +23791,13 @@
     </row>
     <row r="685" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B685" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="C685" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="D685" t="s">
         <v>11</v>
@@ -23814,13 +23817,13 @@
     </row>
     <row r="686" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B686" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="C686" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="D686" t="s">
         <v>11</v>
@@ -23840,10 +23843,10 @@
     </row>
     <row r="687" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="B687" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C687" t="s">
         <v>40</v>
@@ -23866,13 +23869,13 @@
     </row>
     <row r="688" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B688" t="s">
         <v>78</v>
       </c>
       <c r="C688" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="D688" t="s">
         <v>11</v>
@@ -23892,10 +23895,10 @@
     </row>
     <row r="689" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="B689" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="C689" t="s">
         <v>49</v>
@@ -23918,7 +23921,7 @@
     </row>
     <row r="690" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="B690" t="s">
         <v>833</v>
@@ -23944,13 +23947,13 @@
     </row>
     <row r="691" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="B691" t="s">
         <v>49</v>
       </c>
       <c r="C691" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="D691" t="s">
         <v>11</v>
@@ -23970,7 +23973,7 @@
     </row>
     <row r="692" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="B692" t="s">
         <v>320</v>
@@ -23996,13 +23999,13 @@
     </row>
     <row r="693" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="B693" t="s">
         <v>860</v>
       </c>
       <c r="C693" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="D693" t="s">
         <v>11</v>
@@ -24022,13 +24025,13 @@
     </row>
     <row r="694" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="B694" t="s">
         <v>824</v>
       </c>
       <c r="C694" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="D694" t="s">
         <v>11</v>
@@ -24048,7 +24051,7 @@
     </row>
     <row r="695" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="B695" t="s">
         <v>188</v>
@@ -24074,13 +24077,13 @@
     </row>
     <row r="696" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="B696" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="C696" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="D696" t="s">
         <v>11</v>
@@ -24100,13 +24103,13 @@
     </row>
     <row r="697" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="B697" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="C697" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="D697" t="s">
         <v>11</v>
@@ -24126,13 +24129,13 @@
     </row>
     <row r="698" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="B698" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="C698" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="D698" t="s">
         <v>11</v>
@@ -24152,13 +24155,13 @@
     </row>
     <row r="699" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="B699" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="C699" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="D699" t="s">
         <v>11</v>
@@ -24178,13 +24181,13 @@
     </row>
     <row r="700" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="B700" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="C700" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="D700" t="s">
         <v>11</v>
@@ -24204,13 +24207,13 @@
     </row>
     <row r="701" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="B701" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C701" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="D701" t="s">
         <v>11</v>
@@ -24230,13 +24233,13 @@
     </row>
     <row r="702" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="B702" t="s">
         <v>185</v>
       </c>
       <c r="C702" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="D702" t="s">
         <v>11</v>
@@ -24256,13 +24259,13 @@
     </row>
     <row r="703" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="B703" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="C703" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="D703" t="s">
         <v>11</v>
@@ -24282,13 +24285,13 @@
     </row>
     <row r="704" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="B704" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="C704" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="D704" t="s">
         <v>11</v>
@@ -24308,13 +24311,13 @@
     </row>
     <row r="705" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="B705" t="s">
         <v>397</v>
       </c>
       <c r="C705" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="D705" t="s">
         <v>11</v>
@@ -24334,10 +24337,10 @@
     </row>
     <row r="706" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="B706" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="C706" t="s">
         <v>625</v>
@@ -24360,13 +24363,13 @@
     </row>
     <row r="707" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="B707" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="C707" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="D707" t="s">
         <v>11</v>
@@ -24386,13 +24389,13 @@
     </row>
     <row r="708" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="B708" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="C708" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="D708" t="s">
         <v>11</v>
@@ -24412,13 +24415,13 @@
     </row>
     <row r="709" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="B709" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="C709" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="D709" t="s">
         <v>11</v>
@@ -24438,13 +24441,13 @@
     </row>
     <row r="710" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="B710" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="C710" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="D710" t="s">
         <v>11</v>
@@ -24464,13 +24467,13 @@
     </row>
     <row r="711" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="B711" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="C711" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="D711" t="s">
         <v>11</v>
@@ -24490,13 +24493,13 @@
     </row>
     <row r="712" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="B712" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="C712" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="D712" t="s">
         <v>11</v>
@@ -24516,13 +24519,13 @@
     </row>
     <row r="713" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="B713" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="C713" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="D713" t="s">
         <v>11</v>
@@ -24542,13 +24545,13 @@
     </row>
     <row r="714" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="B714" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="C714" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="D714" t="s">
         <v>11</v>
@@ -24568,13 +24571,13 @@
     </row>
     <row r="715" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B715" t="s">
+        <v>1401</v>
+      </c>
+      <c r="C715" t="s">
         <v>1399</v>
-      </c>
-      <c r="B715" t="s">
-        <v>1400</v>
-      </c>
-      <c r="C715" t="s">
-        <v>1398</v>
       </c>
       <c r="D715" t="s">
         <v>11</v>
@@ -24594,13 +24597,13 @@
     </row>
     <row r="716" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="B716" t="s">
         <v>648</v>
       </c>
       <c r="C716" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="D716" t="s">
         <v>11</v>
@@ -24620,13 +24623,13 @@
     </row>
     <row r="717" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="B717" t="s">
         <v>185</v>
       </c>
       <c r="C717" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="D717" t="s">
         <v>11</v>
@@ -24646,7 +24649,7 @@
     </row>
     <row r="718" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="B718" t="s">
         <v>178</v>
@@ -24672,13 +24675,13 @@
     </row>
     <row r="719" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="B719" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="C719" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="D719" t="s">
         <v>11</v>
@@ -24698,13 +24701,13 @@
     </row>
     <row r="720" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B720" t="s">
         <v>1408</v>
       </c>
-      <c r="B720" t="s">
-        <v>1407</v>
-      </c>
       <c r="C720" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="D720" t="s">
         <v>11</v>
@@ -24724,10 +24727,10 @@
     </row>
     <row r="721" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="B721" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="C721" t="s">
         <v>648</v>
@@ -24750,10 +24753,10 @@
     </row>
     <row r="722" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="B722" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="C722" t="s">
         <v>492</v>
@@ -24776,13 +24779,13 @@
     </row>
     <row r="723" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B723" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C723" t="s">
         <v>1414</v>
-      </c>
-      <c r="B723" t="s">
-        <v>1415</v>
-      </c>
-      <c r="C723" t="s">
-        <v>1413</v>
       </c>
       <c r="D723" t="s">
         <v>11</v>
@@ -24802,7 +24805,7 @@
     </row>
     <row r="724" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="B724" t="s">
         <v>726</v>
@@ -24828,13 +24831,13 @@
     </row>
     <row r="725" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="B725" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C725" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="D725" t="s">
         <v>11</v>
@@ -24854,7 +24857,7 @@
     </row>
     <row r="726" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="B726" t="s">
         <v>154</v>
@@ -24880,13 +24883,13 @@
     </row>
     <row r="727" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="B727" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="C727" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="D727" t="s">
         <v>11</v>
@@ -24906,13 +24909,13 @@
     </row>
     <row r="728" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="B728" t="s">
         <v>718</v>
       </c>
       <c r="C728" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="D728" t="s">
         <v>11</v>
@@ -24932,13 +24935,13 @@
     </row>
     <row r="729" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="B729" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="C729" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="D729" t="s">
         <v>11</v>
@@ -24958,13 +24961,13 @@
     </row>
     <row r="730" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="B730" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="C730" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="D730" t="s">
         <v>11</v>
@@ -24984,13 +24987,13 @@
     </row>
     <row r="731" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B731" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="C731" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="D731" t="s">
         <v>11</v>
@@ -25010,10 +25013,10 @@
     </row>
     <row r="732" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="B732" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="C732" t="s">
         <v>605</v>
@@ -25036,10 +25039,10 @@
     </row>
     <row r="733" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B733" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="C733" t="s">
         <v>680</v>
@@ -25062,13 +25065,13 @@
     </row>
     <row r="734" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="B734" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="C734" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="D734" t="s">
         <v>11</v>
@@ -25088,13 +25091,13 @@
     </row>
     <row r="735" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="B735" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="C735" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="D735" t="s">
         <v>11</v>
@@ -25114,7 +25117,7 @@
     </row>
     <row r="736" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="B736" t="s">
         <v>622</v>
@@ -25140,13 +25143,13 @@
     </row>
     <row r="737" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="B737" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="C737" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="D737" t="s">
         <v>11</v>
@@ -25166,10 +25169,10 @@
     </row>
     <row r="738" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="B738" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="C738" t="s">
         <v>492</v>
@@ -25192,13 +25195,13 @@
     </row>
     <row r="739" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="B739" t="s">
         <v>222</v>
       </c>
       <c r="C739" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D739" t="s">
         <v>11</v>
@@ -25218,13 +25221,13 @@
     </row>
     <row r="740" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="B740" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="C740" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="D740" t="s">
         <v>11</v>
@@ -25244,7 +25247,7 @@
     </row>
     <row r="741" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="B741" t="s">
         <v>178</v>
@@ -25270,13 +25273,13 @@
     </row>
     <row r="742" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="B742" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="C742" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="D742" t="s">
         <v>11</v>
@@ -25296,13 +25299,13 @@
     </row>
     <row r="743" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="B743" t="s">
         <v>82</v>
       </c>
       <c r="C743" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D743" t="s">
         <v>11</v>
@@ -25322,13 +25325,13 @@
     </row>
     <row r="744" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="B744" t="s">
         <v>614</v>
       </c>
       <c r="C744" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D744" t="s">
         <v>11</v>
@@ -25348,13 +25351,13 @@
     </row>
     <row r="745" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="B745" t="s">
         <v>510</v>
       </c>
       <c r="C745" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="D745" t="s">
         <v>11</v>
@@ -25374,10 +25377,10 @@
     </row>
     <row r="746" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="B746" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="C746" t="s">
         <v>492</v>
@@ -25400,7 +25403,7 @@
     </row>
     <row r="747" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="B747" t="s">
         <v>100</v>
@@ -25426,10 +25429,10 @@
     </row>
     <row r="748" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="B748" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="C748" t="s">
         <v>492</v>
@@ -25452,13 +25455,13 @@
     </row>
     <row r="749" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="B749" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="C749" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="D749" t="s">
         <v>11</v>
@@ -25478,13 +25481,13 @@
     </row>
     <row r="750" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="B750" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="C750" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="D750" t="s">
         <v>11</v>
@@ -25504,13 +25507,13 @@
     </row>
     <row r="751" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="B751" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="C751" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="D751" t="s">
         <v>11</v>
@@ -25530,13 +25533,13 @@
     </row>
     <row r="752" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B752" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C752" t="s">
         <v>1459</v>
-      </c>
-      <c r="B752" t="s">
-        <v>1095</v>
-      </c>
-      <c r="C752" t="s">
-        <v>1458</v>
       </c>
       <c r="D752" t="s">
         <v>11</v>
@@ -25556,13 +25559,13 @@
     </row>
     <row r="753" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="B753" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="C753" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="D753" t="s">
         <v>11</v>
@@ -25582,13 +25585,13 @@
     </row>
     <row r="754" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="B754" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="C754" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="D754" t="s">
         <v>11</v>
@@ -25608,13 +25611,13 @@
     </row>
     <row r="755" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="B755" t="s">
         <v>365</v>
       </c>
       <c r="C755" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="D755" t="s">
         <v>11</v>
@@ -25634,13 +25637,13 @@
     </row>
     <row r="756" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="B756" t="s">
         <v>83</v>
       </c>
       <c r="C756" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="D756" t="s">
         <v>11</v>
@@ -25660,13 +25663,13 @@
     </row>
     <row r="757" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="B757" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="C757" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="D757" t="s">
         <v>11</v>
@@ -25686,13 +25689,13 @@
     </row>
     <row r="758" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="B758" t="s">
         <v>648</v>
       </c>
       <c r="C758" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="D758" t="s">
         <v>11</v>
@@ -25712,13 +25715,13 @@
     </row>
     <row r="759" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="B759" t="s">
         <v>766</v>
       </c>
       <c r="C759" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="D759" t="s">
         <v>11</v>
@@ -25738,13 +25741,13 @@
     </row>
     <row r="760" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="B760" t="s">
         <v>170</v>
       </c>
       <c r="C760" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="D760" t="s">
         <v>11</v>
@@ -25764,13 +25767,13 @@
     </row>
     <row r="761" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="B761" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="C761" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D761" t="s">
         <v>11</v>
@@ -25790,13 +25793,13 @@
     </row>
     <row r="762" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="B762" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="C762" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="D762" t="s">
         <v>11</v>
@@ -25816,10 +25819,10 @@
     </row>
     <row r="763" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="B763" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="C763" t="s">
         <v>170</v>
@@ -25842,13 +25845,13 @@
     </row>
     <row r="764" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="B764" t="s">
         <v>680</v>
       </c>
       <c r="C764" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="D764" t="s">
         <v>11</v>
@@ -25868,13 +25871,13 @@
     </row>
     <row r="765" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="B765" t="s">
         <v>205</v>
       </c>
       <c r="C765" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="D765" t="s">
         <v>11</v>
@@ -25894,10 +25897,10 @@
     </row>
     <row r="766" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="B766" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="C766" t="s">
         <v>413</v>
@@ -25920,10 +25923,10 @@
     </row>
     <row r="767" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="B767" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="C767" t="s">
         <v>413</v>
@@ -25946,10 +25949,10 @@
     </row>
     <row r="768" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="B768" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="C768" t="s">
         <v>318</v>
@@ -25972,7 +25975,7 @@
     </row>
     <row r="769" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="B769" t="s">
         <v>43</v>
@@ -25998,10 +26001,10 @@
     </row>
     <row r="770" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="B770" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="C770" t="s">
         <v>318</v>
@@ -26024,13 +26027,13 @@
     </row>
     <row r="771" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="B771" t="s">
         <v>57</v>
       </c>
       <c r="C771" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="D771" t="s">
         <v>11</v>
@@ -26050,7 +26053,7 @@
     </row>
     <row r="772" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="B772" t="s">
         <v>333</v>
@@ -26076,13 +26079,13 @@
     </row>
     <row r="773" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="B773" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="C773" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="D773" t="s">
         <v>11</v>
@@ -26102,13 +26105,13 @@
     </row>
     <row r="774" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="B774" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="C774" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="D774" t="s">
         <v>11</v>
@@ -26128,13 +26131,13 @@
     </row>
     <row r="775" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B775" t="s">
+        <v>1495</v>
+      </c>
+      <c r="C775" t="s">
         <v>1493</v>
-      </c>
-      <c r="B775" t="s">
-        <v>1494</v>
-      </c>
-      <c r="C775" t="s">
-        <v>1492</v>
       </c>
       <c r="D775" t="s">
         <v>11</v>
@@ -26154,7 +26157,7 @@
     </row>
     <row r="776" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="B776" t="s">
         <v>172</v>
@@ -26180,13 +26183,13 @@
     </row>
     <row r="777" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="B777" t="s">
         <v>138</v>
       </c>
       <c r="C777" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="D777" t="s">
         <v>11</v>
@@ -26206,13 +26209,13 @@
     </row>
     <row r="778" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="B778" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="C778" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="D778" t="s">
         <v>11</v>
@@ -26232,7 +26235,7 @@
     </row>
     <row r="779" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="B779" t="s">
         <v>680</v>
@@ -26258,10 +26261,10 @@
     </row>
     <row r="780" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="B780" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="C780" t="s">
         <v>71</v>
@@ -26284,7 +26287,7 @@
     </row>
     <row r="781" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="B781" t="s">
         <v>48</v>
@@ -26310,10 +26313,10 @@
     </row>
     <row r="782" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="B782" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="C782" t="s">
         <v>48</v>
@@ -26336,7 +26339,7 @@
     </row>
     <row r="783" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="B783" t="s">
         <v>18</v>
@@ -26362,13 +26365,13 @@
     </row>
     <row r="784" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="B784" t="s">
         <v>299</v>
       </c>
       <c r="C784" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="D784" t="s">
         <v>11</v>
@@ -26388,7 +26391,7 @@
     </row>
     <row r="785" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="B785" t="s">
         <v>353</v>
@@ -26414,10 +26417,10 @@
     </row>
     <row r="786" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="B786" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="C786" t="s">
         <v>299</v>
@@ -26440,7 +26443,7 @@
     </row>
     <row r="787" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="B787" t="s">
         <v>420</v>
@@ -26466,13 +26469,13 @@
     </row>
     <row r="788" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="B788" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="C788" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="D788" t="s">
         <v>11</v>
@@ -26492,13 +26495,13 @@
     </row>
     <row r="789" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="B789" t="s">
         <v>102</v>
       </c>
       <c r="C789" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="D789" t="s">
         <v>11</v>
@@ -26518,10 +26521,10 @@
     </row>
     <row r="790" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="B790" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="C790" t="s">
         <v>563</v>
@@ -26544,10 +26547,10 @@
     </row>
     <row r="791" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="B791" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="C791" t="s">
         <v>369</v>
@@ -26570,10 +26573,10 @@
     </row>
     <row r="792" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="B792" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="C792" t="s">
         <v>745</v>
@@ -26596,13 +26599,13 @@
     </row>
     <row r="793" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="B793" t="s">
         <v>71</v>
       </c>
       <c r="C793" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="D793" t="s">
         <v>11</v>
@@ -26622,10 +26625,10 @@
     </row>
     <row r="794" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="B794" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C794" t="s">
         <v>71</v>
@@ -26648,7 +26651,7 @@
     </row>
     <row r="795" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="B795" t="s">
         <v>82</v>
@@ -26674,13 +26677,13 @@
     </row>
     <row r="796" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="B796" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="C796" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="D796" t="s">
         <v>11</v>
@@ -26700,10 +26703,10 @@
     </row>
     <row r="797" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
+        <v>1531</v>
+      </c>
+      <c r="B797" t="s">
         <v>1530</v>
-      </c>
-      <c r="B797" t="s">
-        <v>1529</v>
       </c>
       <c r="C797" t="s">
         <v>299</v>
@@ -26726,13 +26729,13 @@
     </row>
     <row r="798" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="B798" t="s">
         <v>565</v>
       </c>
       <c r="C798" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="D798" t="s">
         <v>11</v>
@@ -26752,10 +26755,10 @@
     </row>
     <row r="799" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="B799" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="C799" t="s">
         <v>833</v>
@@ -26778,13 +26781,13 @@
     </row>
     <row r="800" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="B800" t="s">
         <v>49</v>
       </c>
       <c r="C800" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="D800" t="s">
         <v>11</v>
@@ -26804,10 +26807,10 @@
     </row>
     <row r="801" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="B801" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="C801" t="s">
         <v>833</v>
@@ -26830,10 +26833,10 @@
     </row>
     <row r="802" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="B802" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="C802" t="s">
         <v>565</v>
@@ -26856,7 +26859,7 @@
     </row>
     <row r="803" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="B803" t="s">
         <v>591</v>
@@ -26882,10 +26885,10 @@
     </row>
     <row r="804" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="B804" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="C804" t="s">
         <v>46</v>
@@ -26908,10 +26911,10 @@
     </row>
     <row r="805" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="B805" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="C805" t="s">
         <v>388</v>
@@ -26934,13 +26937,13 @@
     </row>
     <row r="806" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="B806" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="C806" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="D806" t="s">
         <v>11</v>
@@ -26960,13 +26963,13 @@
     </row>
     <row r="807" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="B807" t="s">
         <v>388</v>
       </c>
       <c r="C807" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="D807" t="s">
         <v>11</v>
@@ -26986,7 +26989,7 @@
     </row>
     <row r="808" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="B808" t="s">
         <v>74</v>
@@ -27012,13 +27015,13 @@
     </row>
     <row r="809" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="B809" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="C809" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="D809" t="s">
         <v>11</v>
@@ -27038,10 +27041,10 @@
     </row>
     <row r="810" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="B810" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="C810" t="s">
         <v>291</v>
@@ -27064,10 +27067,10 @@
     </row>
     <row r="811" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="B811" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="C811" t="s">
         <v>291</v>
@@ -27090,13 +27093,13 @@
     </row>
     <row r="812" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="B812" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="C812" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="D812" t="s">
         <v>11</v>
@@ -27116,10 +27119,10 @@
     </row>
     <row r="813" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="B813" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="C813" t="s">
         <v>291</v>
@@ -27142,7 +27145,7 @@
     </row>
     <row r="814" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="B814" t="s">
         <v>349</v>
@@ -27168,13 +27171,13 @@
     </row>
     <row r="815" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="B815" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="C815" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="D815" t="s">
         <v>11</v>
@@ -27194,10 +27197,10 @@
     </row>
     <row r="816" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="B816" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="C816" t="s">
         <v>349</v>
@@ -27220,7 +27223,7 @@
     </row>
     <row r="817" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="B817" t="s">
         <v>580</v>
@@ -27246,10 +27249,10 @@
     </row>
     <row r="818" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B818" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="C818" t="s">
         <v>341</v>
@@ -27272,10 +27275,10 @@
     </row>
     <row r="819" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="B819" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="C819" t="s">
         <v>341</v>
@@ -27298,13 +27301,13 @@
     </row>
     <row r="820" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="B820" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="C820" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="D820" t="s">
         <v>11</v>
@@ -27324,13 +27327,13 @@
     </row>
     <row r="821" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B821" t="s">
+        <v>876</v>
+      </c>
+      <c r="C821" t="s">
         <v>1569</v>
-      </c>
-      <c r="B821" t="s">
-        <v>875</v>
-      </c>
-      <c r="C821" t="s">
-        <v>1568</v>
       </c>
       <c r="D821" t="s">
         <v>11</v>
@@ -27350,13 +27353,13 @@
     </row>
     <row r="822" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="B822" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="C822" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="D822" t="s">
         <v>11</v>
@@ -27376,13 +27379,13 @@
     </row>
     <row r="823" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="B823" t="s">
         <v>43</v>
       </c>
       <c r="C823" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="D823" t="s">
         <v>11</v>
@@ -27402,10 +27405,10 @@
     </row>
     <row r="824" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="B824" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="C824" t="s">
         <v>43</v>
@@ -27428,13 +27431,13 @@
     </row>
     <row r="825" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="B825" t="s">
         <v>170</v>
       </c>
       <c r="C825" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="D825" t="s">
         <v>11</v>
@@ -27454,13 +27457,13 @@
     </row>
     <row r="826" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="B826" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="C826" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="D826" t="s">
         <v>11</v>
@@ -27480,13 +27483,13 @@
     </row>
     <row r="827" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="B827" t="s">
         <v>680</v>
       </c>
       <c r="C827" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D827" t="s">
         <v>11</v>
@@ -27506,10 +27509,10 @@
     </row>
     <row r="828" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="B828" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="C828" t="s">
         <v>680</v>
@@ -27532,13 +27535,13 @@
     </row>
     <row r="829" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="B829" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="C829" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="D829" t="s">
         <v>11</v>
@@ -27558,10 +27561,10 @@
     </row>
     <row r="830" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="B830" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="C830" t="s">
         <v>170</v>
@@ -27584,10 +27587,10 @@
     </row>
     <row r="831" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="B831" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="C831" t="s">
         <v>667</v>
@@ -27610,10 +27613,10 @@
     </row>
     <row r="832" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="B832" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="C832" t="s">
         <v>551</v>
@@ -27636,7 +27639,7 @@
     </row>
     <row r="833" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="B833" t="s">
         <v>156</v>
@@ -27662,7 +27665,7 @@
     </row>
     <row r="834" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="B834" t="s">
         <v>388</v>
@@ -27688,10 +27691,10 @@
     </row>
     <row r="835" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="B835" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="C835" t="s">
         <v>156</v>
@@ -27714,7 +27717,7 @@
     </row>
     <row r="836" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="B836" t="s">
         <v>154</v>
@@ -27740,13 +27743,13 @@
     </row>
     <row r="837" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="B837" t="s">
         <v>431</v>
       </c>
       <c r="C837" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="D837" t="s">
         <v>11</v>
@@ -27766,7 +27769,7 @@
     </row>
     <row r="838" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="B838" t="s">
         <v>48</v>
@@ -27792,7 +27795,7 @@
     </row>
     <row r="839" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="B839" t="s">
         <v>686</v>
@@ -27818,10 +27821,10 @@
     </row>
     <row r="840" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="B840" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="C840" t="s">
         <v>156</v>
@@ -27844,10 +27847,10 @@
     </row>
     <row r="841" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B841" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="C841" t="s">
         <v>566</v>
@@ -27870,10 +27873,10 @@
     </row>
     <row r="842" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="B842" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="C842" t="s">
         <v>95</v>
@@ -27896,7 +27899,7 @@
     </row>
     <row r="843" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="B843" t="s">
         <v>269</v>
@@ -27922,10 +27925,10 @@
     </row>
     <row r="844" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="B844" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="C844" t="s">
         <v>269</v>
@@ -27948,13 +27951,13 @@
     </row>
     <row r="845" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="B845" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="C845" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="D845" t="s">
         <v>11</v>
@@ -27974,7 +27977,7 @@
     </row>
     <row r="846" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="B846" t="s">
         <v>76</v>
@@ -28000,7 +28003,7 @@
     </row>
     <row r="847" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="B847" t="s">
         <v>313</v>
@@ -28026,13 +28029,13 @@
     </row>
     <row r="848" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="B848" t="s">
         <v>86</v>
       </c>
       <c r="C848" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="D848" t="s">
         <v>11</v>
@@ -28052,10 +28055,10 @@
     </row>
     <row r="849" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="B849" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="C849" t="s">
         <v>313</v>
@@ -28078,13 +28081,13 @@
     </row>
     <row r="850" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="B850" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="C850" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="D850" t="s">
         <v>11</v>
@@ -28104,10 +28107,10 @@
     </row>
     <row r="851" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="B851" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="C851" t="s">
         <v>86</v>
@@ -28130,10 +28133,10 @@
     </row>
     <row r="852" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="B852" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="C852" t="s">
         <v>228</v>
@@ -28156,7 +28159,7 @@
     </row>
     <row r="853" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="B853" t="s">
         <v>462</v>
@@ -28182,7 +28185,7 @@
     </row>
     <row r="854" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="B854" t="s">
         <v>239</v>
@@ -28208,7 +28211,7 @@
     </row>
     <row r="855" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="B855" t="s">
         <v>420</v>
@@ -28234,13 +28237,13 @@
     </row>
     <row r="856" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="B856" t="s">
         <v>320</v>
       </c>
       <c r="C856" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="D856" t="s">
         <v>11</v>
@@ -28260,7 +28263,7 @@
     </row>
     <row r="857" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="B857" t="s">
         <v>333</v>
@@ -28286,13 +28289,13 @@
     </row>
     <row r="858" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="B858" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="C858" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="D858" t="s">
         <v>11</v>
@@ -28312,13 +28315,13 @@
     </row>
     <row r="859" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="B859" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="C859" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="D859" t="s">
         <v>11</v>
@@ -28338,13 +28341,13 @@
     </row>
     <row r="860" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="B860" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="C860" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="D860" t="s">
         <v>11</v>
@@ -28364,13 +28367,13 @@
     </row>
     <row r="861" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="B861" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="C861" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="D861" t="s">
         <v>11</v>
@@ -28390,13 +28393,13 @@
     </row>
     <row r="862" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="B862" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="C862" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="D862" t="s">
         <v>11</v>
@@ -28416,13 +28419,13 @@
     </row>
     <row r="863" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
+        <v>1632</v>
+      </c>
+      <c r="B863" t="s">
+        <v>1633</v>
+      </c>
+      <c r="C863" t="s">
         <v>1631</v>
-      </c>
-      <c r="B863" t="s">
-        <v>1632</v>
-      </c>
-      <c r="C863" t="s">
-        <v>1630</v>
       </c>
       <c r="D863" t="s">
         <v>11</v>
@@ -28442,7 +28445,7 @@
     </row>
     <row r="864" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="B864" t="s">
         <v>550</v>
@@ -28468,13 +28471,13 @@
     </row>
     <row r="865" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="B865" t="s">
         <v>462</v>
       </c>
       <c r="C865" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="D865" t="s">
         <v>11</v>
@@ -28494,13 +28497,13 @@
     </row>
     <row r="866" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="B866" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="C866" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="D866" t="s">
         <v>11</v>
@@ -28520,7 +28523,7 @@
     </row>
     <row r="867" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A867" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="B867" t="s">
         <v>156</v>
@@ -28546,7 +28549,7 @@
     </row>
     <row r="868" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="B868" t="s">
         <v>776</v>
@@ -28572,7 +28575,7 @@
     </row>
     <row r="869" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="B869" t="s">
         <v>417</v>
@@ -28598,13 +28601,13 @@
     </row>
     <row r="870" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="B870" t="s">
         <v>738</v>
       </c>
       <c r="C870" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="D870" t="s">
         <v>11</v>
@@ -28624,13 +28627,13 @@
     </row>
     <row r="871" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A871" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="B871" t="s">
         <v>9</v>
       </c>
       <c r="C871" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="D871" t="s">
         <v>11</v>
@@ -28650,13 +28653,13 @@
     </row>
     <row r="872" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B872" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="C872" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="D872" t="s">
         <v>11</v>
@@ -28676,13 +28679,13 @@
     </row>
     <row r="873" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A873" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="B873" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="C873" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="D873" t="s">
         <v>11</v>
@@ -28702,13 +28705,13 @@
     </row>
     <row r="874" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A874" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="B874" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C874" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="D874" t="s">
         <v>11</v>
@@ -28728,13 +28731,13 @@
     </row>
     <row r="875" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="B875" t="s">
         <v>373</v>
       </c>
       <c r="C875" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="D875" t="s">
         <v>11</v>
@@ -28754,10 +28757,10 @@
     </row>
     <row r="876" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A876" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="B876" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C876" t="s">
         <v>92</v>
@@ -28780,7 +28783,7 @@
     </row>
     <row r="877" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="B877" t="s">
         <v>232</v>
@@ -28806,13 +28809,13 @@
     </row>
     <row r="878" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A878" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="B878" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="C878" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="D878" t="s">
         <v>11</v>
@@ -28832,13 +28835,13 @@
     </row>
     <row r="879" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="B879" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="C879" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="D879" t="s">
         <v>11</v>
@@ -28858,7 +28861,7 @@
     </row>
     <row r="880" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="B880" t="s">
         <v>581</v>
@@ -28884,7 +28887,7 @@
     </row>
     <row r="881" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A881" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="B881" t="s">
         <v>74</v>
@@ -28910,13 +28913,13 @@
     </row>
     <row r="882" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="B882" t="s">
         <v>565</v>
       </c>
       <c r="C882" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="D882" t="s">
         <v>11</v>
@@ -28936,13 +28939,13 @@
     </row>
     <row r="883" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
+        <v>1659</v>
+      </c>
+      <c r="B883" t="s">
+        <v>1660</v>
+      </c>
+      <c r="C883" t="s">
         <v>1658</v>
-      </c>
-      <c r="B883" t="s">
-        <v>1659</v>
-      </c>
-      <c r="C883" t="s">
-        <v>1657</v>
       </c>
       <c r="D883" t="s">
         <v>11</v>
@@ -28962,10 +28965,10 @@
     </row>
     <row r="884" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="B884" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="C884" t="s">
         <v>170</v>
@@ -28988,10 +28991,10 @@
     </row>
     <row r="885" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A885" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="B885" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="C885" t="s">
         <v>565</v>
@@ -29014,13 +29017,13 @@
     </row>
     <row r="886" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="B886" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="C886" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="D886" t="s">
         <v>11</v>
@@ -29040,13 +29043,13 @@
     </row>
     <row r="887" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B887" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="C887" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="D887" t="s">
         <v>11</v>
@@ -29066,13 +29069,13 @@
     </row>
     <row r="888" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="B888" t="s">
         <v>660</v>
       </c>
       <c r="C888" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="D888" t="s">
         <v>11</v>
@@ -29092,7 +29095,7 @@
     </row>
     <row r="889" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A889" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="B889" t="s">
         <v>297</v>
@@ -29118,10 +29121,10 @@
     </row>
     <row r="890" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A890" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="B890" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="C890" t="s">
         <v>605</v>
@@ -29144,13 +29147,13 @@
     </row>
     <row r="891" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="B891" t="s">
         <v>265</v>
       </c>
       <c r="C891" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="D891" t="s">
         <v>11</v>
@@ -29170,10 +29173,10 @@
     </row>
     <row r="892" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="B892" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="C892" t="s">
         <v>605</v>
@@ -29196,10 +29199,10 @@
     </row>
     <row r="893" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="B893" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="C893" t="s">
         <v>46</v>
@@ -29222,13 +29225,13 @@
     </row>
     <row r="894" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="B894" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="C894" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="D894" t="s">
         <v>11</v>
@@ -29248,10 +29251,10 @@
     </row>
     <row r="895" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A895" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="B895" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="C895" t="s">
         <v>592</v>
@@ -29274,13 +29277,13 @@
     </row>
     <row r="896" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="B896" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="C896" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="D896" t="s">
         <v>11</v>
@@ -29300,13 +29303,13 @@
     </row>
     <row r="897" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A897" t="s">
+        <v>1684</v>
+      </c>
+      <c r="B897" t="s">
+        <v>1685</v>
+      </c>
+      <c r="C897" t="s">
         <v>1683</v>
-      </c>
-      <c r="B897" t="s">
-        <v>1684</v>
-      </c>
-      <c r="C897" t="s">
-        <v>1682</v>
       </c>
       <c r="D897" t="s">
         <v>11</v>
@@ -29326,13 +29329,13 @@
     </row>
     <row r="898" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A898" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="B898" t="s">
         <v>614</v>
       </c>
       <c r="C898" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="D898" t="s">
         <v>11</v>
@@ -29352,10 +29355,10 @@
     </row>
     <row r="899" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="B899" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="C899" t="s">
         <v>614</v>
@@ -29378,13 +29381,13 @@
     </row>
     <row r="900" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="B900" t="s">
         <v>369</v>
       </c>
       <c r="C900" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="D900" t="s">
         <v>11</v>
@@ -29404,7 +29407,7 @@
     </row>
     <row r="901" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A901" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="B901" t="s">
         <v>510</v>
@@ -29430,13 +29433,13 @@
     </row>
     <row r="902" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A902" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="B902" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="C902" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="D902" t="s">
         <v>11</v>
@@ -29456,10 +29459,10 @@
     </row>
     <row r="903" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A903" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="B903" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="C903" t="s">
         <v>369</v>
@@ -29482,13 +29485,13 @@
     </row>
     <row r="904" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A904" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="B904" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="C904" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="D904" t="s">
         <v>11</v>
@@ -29508,7 +29511,7 @@
     </row>
     <row r="905" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A905" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="B905" t="s">
         <v>46</v>
@@ -29534,10 +29537,10 @@
     </row>
     <row r="906" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A906" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="B906" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="C906" t="s">
         <v>46</v>
@@ -29560,7 +29563,7 @@
     </row>
     <row r="907" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="B907" t="s">
         <v>565</v>
@@ -29586,13 +29589,13 @@
     </row>
     <row r="908" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A908" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="B908" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="C908" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="D908" t="s">
         <v>11</v>
@@ -29612,13 +29615,13 @@
     </row>
     <row r="909" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A909" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="B909" t="s">
         <v>563</v>
       </c>
       <c r="C909" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="D909" t="s">
         <v>11</v>
@@ -29638,7 +29641,7 @@
     </row>
     <row r="910" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A910" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="B910" t="s">
         <v>428</v>
@@ -29664,13 +29667,13 @@
     </row>
     <row r="911" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A911" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="B911" t="s">
         <v>356</v>
       </c>
       <c r="C911" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="D911" t="s">
         <v>11</v>
@@ -29690,10 +29693,10 @@
     </row>
     <row r="912" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A912" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="B912" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="C912" t="s">
         <v>46</v>
@@ -29716,13 +29719,13 @@
     </row>
     <row r="913" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A913" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="B913" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="C913" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="D913" t="s">
         <v>11</v>
@@ -29742,10 +29745,10 @@
     </row>
     <row r="914" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A914" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="B914" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="C914" t="s">
         <v>356</v>
@@ -29768,10 +29771,10 @@
     </row>
     <row r="915" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A915" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="B915" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="C915" t="s">
         <v>407</v>
@@ -29794,13 +29797,13 @@
     </row>
     <row r="916" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="B916" t="s">
         <v>383</v>
       </c>
       <c r="C916" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="D916" t="s">
         <v>11</v>
@@ -29820,10 +29823,10 @@
     </row>
     <row r="917" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A917" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="B917" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="C917" t="s">
         <v>407</v>
@@ -29846,13 +29849,13 @@
     </row>
     <row r="918" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A918" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="B918" t="s">
         <v>413</v>
       </c>
       <c r="C918" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="D918" t="s">
         <v>11</v>
@@ -29872,10 +29875,10 @@
     </row>
     <row r="919" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A919" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="B919" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="C919" t="s">
         <v>413</v>
@@ -29898,10 +29901,10 @@
     </row>
     <row r="920" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A920" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="B920" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="C920" t="s">
         <v>413</v>
@@ -29924,13 +29927,13 @@
     </row>
     <row r="921" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A921" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="B921" t="s">
         <v>420</v>
       </c>
       <c r="C921" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="D921" t="s">
         <v>11</v>
@@ -29950,13 +29953,13 @@
     </row>
     <row r="922" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A922" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="B922" t="s">
         <v>21</v>
       </c>
       <c r="C922" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="D922" t="s">
         <v>11</v>
@@ -29976,7 +29979,7 @@
     </row>
     <row r="923" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A923" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="B923" t="s">
         <v>333</v>
@@ -30002,13 +30005,13 @@
     </row>
     <row r="924" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A924" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="B924" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="C924" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="D924" t="s">
         <v>11</v>
@@ -30028,10 +30031,10 @@
     </row>
     <row r="925" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A925" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="B925" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="C925" t="s">
         <v>222</v>
@@ -30054,10 +30057,10 @@
     </row>
     <row r="926" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A926" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="B926" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="C926" t="s">
         <v>49</v>
@@ -30080,10 +30083,10 @@
     </row>
     <row r="927" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A927" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="B927" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="C927" t="s">
         <v>71</v>
@@ -30106,13 +30109,13 @@
     </row>
     <row r="928" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A928" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="B928" t="s">
         <v>282</v>
       </c>
       <c r="C928" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="D928" t="s">
         <v>11</v>
@@ -30132,13 +30135,13 @@
     </row>
     <row r="929" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A929" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="B929" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="C929" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="D929" t="s">
         <v>11</v>
@@ -30158,10 +30161,10 @@
     </row>
     <row r="930" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A930" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="B930" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="C930" t="s">
         <v>268</v>
@@ -30184,13 +30187,13 @@
     </row>
     <row r="931" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A931" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="B931" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="C931" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="D931" t="s">
         <v>11</v>
@@ -30210,7 +30213,7 @@
     </row>
     <row r="932" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A932" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="B932" t="s">
         <v>702</v>
@@ -30236,13 +30239,13 @@
     </row>
     <row r="933" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A933" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="B933" t="s">
         <v>591</v>
       </c>
       <c r="C933" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="D933" t="s">
         <v>11</v>
@@ -30262,7 +30265,7 @@
     </row>
     <row r="934" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A934" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="B934" t="s">
         <v>433</v>
@@ -30288,13 +30291,13 @@
     </row>
     <row r="935" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A935" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="B935" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="C935" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="D935" t="s">
         <v>11</v>
@@ -30314,13 +30317,13 @@
     </row>
     <row r="936" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A936" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="B936" t="s">
         <v>723</v>
       </c>
       <c r="C936" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="D936" t="s">
         <v>11</v>
@@ -30340,13 +30343,13 @@
     </row>
     <row r="937" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A937" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="B937" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="C937" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="D937" t="s">
         <v>11</v>
@@ -30366,13 +30369,13 @@
     </row>
     <row r="938" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A938" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="B938" t="s">
         <v>21</v>
       </c>
       <c r="C938" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="D938" t="s">
         <v>11</v>
@@ -30392,10 +30395,10 @@
     </row>
     <row r="939" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A939" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B939" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="C939" t="s">
         <v>735</v>
@@ -30418,13 +30421,13 @@
     </row>
     <row r="940" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A940" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="B940" t="s">
         <v>232</v>
       </c>
       <c r="C940" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="D940" t="s">
         <v>11</v>
@@ -30444,10 +30447,10 @@
     </row>
     <row r="941" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A941" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="B941" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="C941" t="s">
         <v>263</v>
@@ -30470,10 +30473,10 @@
     </row>
     <row r="942" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A942" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="B942" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="C942" t="s">
         <v>663</v>
@@ -30496,10 +30499,10 @@
     </row>
     <row r="943" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A943" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="B943" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="C943" t="s">
         <v>21</v>
@@ -30522,7 +30525,7 @@
     </row>
     <row r="944" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A944" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="B944" t="s">
         <v>18</v>
@@ -30548,10 +30551,10 @@
     </row>
     <row r="945" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A945" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="B945" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="C945" t="s">
         <v>18</v>
@@ -30574,13 +30577,13 @@
     </row>
     <row r="946" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A946" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="B946" t="s">
         <v>385</v>
       </c>
       <c r="C946" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="D946" t="s">
         <v>11</v>
@@ -30600,13 +30603,13 @@
     </row>
     <row r="947" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A947" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="B947" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="C947" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="D947" t="s">
         <v>11</v>
@@ -30626,7 +30629,7 @@
     </row>
     <row r="948" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A948" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="B948" t="s">
         <v>686</v>
@@ -30652,7 +30655,7 @@
     </row>
     <row r="949" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A949" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="B949" t="s">
         <v>728</v>
@@ -30678,13 +30681,13 @@
     </row>
     <row r="950" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A950" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="B950" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="C950" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="D950" t="s">
         <v>11</v>
@@ -30704,13 +30707,13 @@
     </row>
     <row r="951" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A951" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="B951" t="s">
         <v>185</v>
       </c>
       <c r="C951" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="D951" t="s">
         <v>11</v>
@@ -30730,13 +30733,13 @@
     </row>
     <row r="952" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A952" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="B952" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="C952" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="D952" t="s">
         <v>11</v>
@@ -30756,13 +30759,13 @@
     </row>
     <row r="953" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A953" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="B953" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="C953" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="D953" t="s">
         <v>11</v>
@@ -30782,13 +30785,13 @@
     </row>
     <row r="954" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A954" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="B954" t="s">
         <v>766</v>
       </c>
       <c r="C954" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="D954" t="s">
         <v>11</v>
@@ -30808,13 +30811,13 @@
     </row>
     <row r="955" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A955" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="B955" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="C955" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="D955" t="s">
         <v>11</v>
@@ -30834,7 +30837,7 @@
     </row>
     <row r="956" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A956" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="B956" t="s">
         <v>172</v>
@@ -30860,13 +30863,13 @@
     </row>
     <row r="957" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A957" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="B957" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="C957" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="D957" t="s">
         <v>11</v>
@@ -30886,13 +30889,13 @@
     </row>
     <row r="958" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A958" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="B958" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="C958" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="D958" t="s">
         <v>11</v>
@@ -30912,13 +30915,13 @@
     </row>
     <row r="959" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A959" t="s">
+        <v>1790</v>
+      </c>
+      <c r="B959" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C959" t="s">
         <v>1789</v>
-      </c>
-      <c r="B959" t="s">
-        <v>1790</v>
-      </c>
-      <c r="C959" t="s">
-        <v>1788</v>
       </c>
       <c r="D959" t="s">
         <v>11</v>
@@ -30938,13 +30941,13 @@
     </row>
     <row r="960" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A960" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="B960" t="s">
         <v>222</v>
       </c>
       <c r="C960" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="D960" t="s">
         <v>11</v>
@@ -30964,13 +30967,13 @@
     </row>
     <row r="961" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A961" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="B961" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="C961" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="D961" t="s">
         <v>11</v>
@@ -30990,13 +30993,13 @@
     </row>
     <row r="962" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A962" t="s">
+        <v>1796</v>
+      </c>
+      <c r="B962" t="s">
+        <v>1580</v>
+      </c>
+      <c r="C962" t="s">
         <v>1795</v>
-      </c>
-      <c r="B962" t="s">
-        <v>1579</v>
-      </c>
-      <c r="C962" t="s">
-        <v>1794</v>
       </c>
       <c r="D962" t="s">
         <v>11</v>
@@ -31016,13 +31019,13 @@
     </row>
     <row r="963" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A963" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="B963" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="C963" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="D963" t="s">
         <v>11</v>
@@ -31042,10 +31045,10 @@
     </row>
     <row r="964" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A964" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="B964" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="C964" t="s">
         <v>222</v>
@@ -31068,10 +31071,10 @@
     </row>
     <row r="965" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A965" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="B965" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="C965" t="s">
         <v>763</v>
@@ -31094,13 +31097,13 @@
     </row>
     <row r="966" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A966" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="B966" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="C966" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="D966" t="s">
         <v>11</v>
@@ -31120,7 +31123,7 @@
     </row>
     <row r="967" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A967" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="B967" t="s">
         <v>46</v>
@@ -31146,13 +31149,13 @@
     </row>
     <row r="968" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A968" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="B968" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="C968" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="D968" t="s">
         <v>11</v>
@@ -31172,10 +31175,10 @@
     </row>
     <row r="969" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A969" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="B969" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="C969" t="s">
         <v>46</v>
@@ -31198,13 +31201,13 @@
     </row>
     <row r="970" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A970" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="B970" t="s">
         <v>846</v>
       </c>
       <c r="C970" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="D970" t="s">
         <v>11</v>
@@ -31224,13 +31227,13 @@
     </row>
     <row r="971" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A971" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="B971" t="s">
         <v>411</v>
       </c>
       <c r="C971" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="D971" t="s">
         <v>11</v>
@@ -31250,7 +31253,7 @@
     </row>
     <row r="972" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A972" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="B972" t="s">
         <v>100</v>
@@ -31276,7 +31279,7 @@
     </row>
     <row r="973" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A973" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B973" t="s">
         <v>558</v>
@@ -31302,13 +31305,13 @@
     </row>
     <row r="974" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A974" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="B974" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="C974" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="D974" t="s">
         <v>11</v>
@@ -31328,13 +31331,13 @@
     </row>
     <row r="975" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A975" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="B975" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="C975" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="D975" t="s">
         <v>11</v>
@@ -31354,13 +31357,13 @@
     </row>
     <row r="976" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A976" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="B976" t="s">
         <v>558</v>
       </c>
       <c r="C976" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="D976" t="s">
         <v>11</v>
@@ -31380,13 +31383,13 @@
     </row>
     <row r="977" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A977" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="B977" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="C977" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="D977" t="s">
         <v>11</v>
@@ -31406,7 +31409,7 @@
     </row>
     <row r="978" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A978" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="B978" t="s">
         <v>756</v>
@@ -31432,7 +31435,7 @@
     </row>
     <row r="979" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A979" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="B979" t="s">
         <v>420</v>
@@ -31458,10 +31461,10 @@
     </row>
     <row r="980" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A980" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="B980" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="C980" t="s">
         <v>756</v>
@@ -31484,13 +31487,13 @@
     </row>
     <row r="981" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A981" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="B981" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="C981" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="D981" t="s">
         <v>11</v>
@@ -31510,7 +31513,7 @@
     </row>
     <row r="982" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A982" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="B982" t="s">
         <v>246</v>
@@ -31536,13 +31539,13 @@
     </row>
     <row r="983" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A983" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="B983" t="s">
         <v>45</v>
       </c>
       <c r="C983" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="D983" t="s">
         <v>11</v>
@@ -31562,7 +31565,7 @@
     </row>
     <row r="984" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A984" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="B984" t="s">
         <v>333</v>
@@ -31588,13 +31591,13 @@
     </row>
     <row r="985" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A985" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="B985" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="C985" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="D985" t="s">
         <v>11</v>
@@ -31614,7 +31617,7 @@
     </row>
     <row r="986" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A986" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="B986" t="s">
         <v>30</v>
@@ -31640,10 +31643,10 @@
     </row>
     <row r="987" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A987" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="B987" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="C987" t="s">
         <v>30</v>
@@ -31666,13 +31669,13 @@
     </row>
     <row r="988" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A988" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="B988" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="C988" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="D988" t="s">
         <v>11</v>
@@ -31692,7 +31695,7 @@
     </row>
     <row r="989" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A989" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="B989" t="s">
         <v>669</v>
@@ -31718,13 +31721,13 @@
     </row>
     <row r="990" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A990" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="B990" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C990" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="D990" t="s">
         <v>11</v>
@@ -31744,10 +31747,10 @@
     </row>
     <row r="991" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A991" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="B991" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="C991" t="s">
         <v>299</v>
@@ -31770,7 +31773,7 @@
     </row>
     <row r="992" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A992" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="B992" t="s">
         <v>706</v>
@@ -31796,10 +31799,10 @@
     </row>
     <row r="993" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A993" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="B993" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="C993" t="s">
         <v>822</v>
@@ -31822,7 +31825,7 @@
     </row>
     <row r="994" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A994" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="B994" t="s">
         <v>276</v>
@@ -31848,7 +31851,7 @@
     </row>
     <row r="995" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A995" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="B995" t="s">
         <v>565</v>
@@ -31874,10 +31877,10 @@
     </row>
     <row r="996" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A996" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="B996" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="C996" t="s">
         <v>92</v>
@@ -31900,13 +31903,13 @@
     </row>
     <row r="997" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A997" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="B997" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="C997" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="D997" t="s">
         <v>11</v>
@@ -31926,10 +31929,10 @@
     </row>
     <row r="998" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A998" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="B998" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="C998" t="s">
         <v>718</v>
@@ -31952,7 +31955,7 @@
     </row>
     <row r="999" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A999" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B999" t="s">
         <v>265</v>
@@ -31978,13 +31981,13 @@
     </row>
     <row r="1000" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1000" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="B1000" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="C1000" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="D1000" t="s">
         <v>11</v>
@@ -32004,13 +32007,13 @@
     </row>
     <row r="1001" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1001" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="B1001" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="C1001" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="D1001" t="s">
         <v>11</v>
@@ -32030,13 +32033,13 @@
     </row>
     <row r="1002" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1002" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="B1002" t="s">
         <v>21</v>
       </c>
       <c r="C1002" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="D1002" t="s">
         <v>11</v>
@@ -32056,7 +32059,7 @@
     </row>
     <row r="1003" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1003" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="B1003" t="s">
         <v>246</v>
@@ -32082,7 +32085,7 @@
     </row>
     <row r="1004" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1004" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B1004" t="s">
         <v>380</v>
@@ -32108,10 +32111,10 @@
     </row>
     <row r="1005" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1005" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="B1005" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="C1005" t="s">
         <v>228</v>
@@ -32134,13 +32137,13 @@
     </row>
     <row r="1006" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1006" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="B1006" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="C1006" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="D1006" t="s">
         <v>11</v>
